--- a/data/raw/chip/cms21/SOURCE_MANIFEST.xlsx
+++ b/data/raw/chip/cms21/SOURCE_MANIFEST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\washington-county-federal-fiscal-balance\data\raw\chip\cms21\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4D019410-25AB-4A87-9E10-E98D345FCF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E939C3B8-007C-4584-A30E-3D674FD62CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABF22315-93FD-45AD-8450-50FF93B46BAF}"/>
   </bookViews>
